--- a/paper results/7. CDC diabetes dataset/TRTR_TSTR_results_cdc_diabetes.xlsx
+++ b/paper results/7. CDC diabetes dataset/TRTR_TSTR_results_cdc_diabetes.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Summary" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CTGAN" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="CopulaGAN" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TVAE" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="GaussianCopula" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="WGAN_GP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="CTABGAN" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="TabDDPM" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ForestDiffusion" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRTR_Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All_Comparisons" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTGAN" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CopulaGAN" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TVAE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GaussianCopula" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WGAN_GP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CTABGAN" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TabDDPM" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ForestDiffusion" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,13 +27,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -44,7 +47,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -52,12 +55,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -427,67 +439,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)</t>
         </is>
@@ -1018,152 +1030,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -1172,108 +1184,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8653850720278614</v>
+        <v>0.8965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004897208981754782</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1722933021134507</v>
+        <v>0.8800945612919768</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004133046767167164</v>
+        <v>0.01557076241163555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6012194836101217</v>
+        <v>0.8849723263768654</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01161315896115709</v>
+        <v>0.01637849998720951</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1005681011219997</v>
+        <v>0.8965</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002743294672201886</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8654 ± 0.0005</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1723 ± 0.0041</t>
+          <t>0.8801 ± 0.0156</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.6012 ± 0.0116</t>
+          <t>0.8850 ± 0.0164</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.1006 ± 0.0027</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.8555406047174292</v>
+        <v>0.865</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00377696765177999</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009733384613800168</v>
+        <v>0.8023860589812333</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.006780845959806028</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.1303637540525382</v>
+        <v>0.7482249999999999</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0703114812688721</v>
+        <v>1.1702778228589e-16</v>
       </c>
       <c r="T2" t="n">
-        <v>0.005169720210197415</v>
+        <v>0.865</v>
       </c>
       <c r="U2" t="n">
-        <v>0.003746991905084153</v>
+        <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.8555 ± 0.0038</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.0097 ± 0.0068</t>
+          <t>0.8024 ± 0.0000</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.1304 ± 0.0703</t>
+          <t>0.7482 ± 0.0000</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.0052 ± 0.0037</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.009844467310432203</v>
+        <v>0.03149999999999997</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.1625599174996505</v>
+        <v>0.07770850231074355</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.4708557295575835</v>
+        <v>0.1367473263768655</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.09539838091180228</v>
+        <v>0.03149999999999997</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -1284,108 +1296,108 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8644649358872882</v>
+        <v>0.8905</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001292019377334109</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2639376061713777</v>
+        <v>0.8613575595536576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0296521977876718</v>
+        <v>0.00835629357808527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5445815044621426</v>
+        <v>0.8875770769739587</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01990884968502404</v>
+        <v>0.009319454743331457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1754864365857122</v>
+        <v>0.8905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02609605447626427</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8645 ± 0.0013</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2639 ± 0.0297</t>
+          <t>0.8614 ± 0.0084</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.5446 ± 0.0199</t>
+          <t>0.8876 ± 0.0093</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.1755 ± 0.0261</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.8481953458920373</v>
+        <v>0.8625</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00515717857077356</v>
+        <v>0.003535533905932741</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03961698089772425</v>
+        <v>0.8011379217986173</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01568461328391349</v>
+        <v>0.001766402176797399</v>
       </c>
       <c r="R3" t="n">
-        <v>0.1702923936811873</v>
+        <v>0.7479310027409777</v>
       </c>
       <c r="S3" t="n">
-        <v>0.02442399879718625</v>
+        <v>0.0004163356235445011</v>
       </c>
       <c r="T3" t="n">
-        <v>0.02289447521658855</v>
+        <v>0.8625</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01039500870734086</v>
+        <v>0.003535533905932741</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.8482 ± 0.0052</t>
+          <t>0.8625 ± 0.0035</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.0396 ± 0.0157</t>
+          <t>0.8011 ± 0.0018</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.1703 ± 0.0244</t>
+          <t>0.7479 ± 0.0004</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.0229 ± 0.0104</t>
+          <t>0.8625 ± 0.0035</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.01626958999525097</v>
+        <v>0.02799999999999991</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.2243206252736535</v>
+        <v>0.06021963775504025</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.3742891107809553</v>
+        <v>0.139646074232981</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.1525919613691237</v>
+        <v>0.02799999999999991</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -1400,104 +1412,104 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8635903118568941</v>
+        <v>0.8815</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003809564049741432</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.121804936464582</v>
+        <v>0.8395197032079371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00369981836688605</v>
+        <v>0.007183950573405901</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.8927447421022293</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01145382697210849</v>
+        <v>0.01169636211175201</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06790228660701605</v>
+        <v>0.8815</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002191473549437678</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8636 ± 0.0004</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1218 ± 0.0037</t>
+          <t>0.8395 ± 0.0072</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5911 ± 0.0115</t>
+          <t>0.8927 ± 0.0117</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0679 ± 0.0022</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.8606735792306475</v>
+        <v>0.865</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>0.8023860589812333</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.7482249999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.1702778228589e-16</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.865</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.8607 ± 0.0000</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.0000 ± 0.0000</t>
+          <t>0.8024 ± 0.0000</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0000 ± 0.0000</t>
+          <t>0.7482 ± 0.0000</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.0000 ± 0.0000</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.002916732626246588</v>
+        <v>0.01649999999999996</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.121804936464582</v>
+        <v>0.03713364422670384</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.1445197421022294</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.06790228660701605</v>
+        <v>0.01649999999999996</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -1508,108 +1520,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8635467785341143</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007481700690606898</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2388691165223189</v>
+        <v>0.8460496521431005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004564487931064464</v>
+        <v>0.01294479429530151</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5359686608772588</v>
+        <v>0.865010991243126</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00934558839892455</v>
+        <v>0.02161817607890089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1536855560289732</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003128072545874311</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8635 ± 0.0007</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.2389 ± 0.0046</t>
+          <t>0.8460 ± 0.0129</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5360 ± 0.0093</t>
+          <t>0.8650 ± 0.0216</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.1537 ± 0.0031</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.8601393066328953</v>
+        <v>0.8634999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0005102049190908339</v>
+        <v>0.003374742788552767</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001013054635224362</v>
+        <v>0.8016366389712081</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001075337642532265</v>
+        <v>0.001686805320122046</v>
       </c>
       <c r="R5" t="n">
-        <v>0.08009597637504615</v>
+        <v>0.7480483645500228</v>
       </c>
       <c r="S5" t="n">
-        <v>0.05699063662778444</v>
+        <v>0.0003977256889716439</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0005112910097997443</v>
+        <v>0.8634999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0005434207206280071</v>
+        <v>0.003374742788552767</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.8601 ± 0.0005</t>
+          <t>0.8635 ± 0.0034</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0010 ± 0.0011</t>
+          <t>0.8016 ± 0.0017</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0801 ± 0.0570</t>
+          <t>0.7480 ± 0.0004</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.0005 ± 0.0005</t>
+          <t>0.8635 ± 0.0034</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.003407471901219039</v>
+        <v>0.01650000000000018</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.2378560618870945</v>
+        <v>0.04441301317189239</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.4558726845022126</v>
+        <v>0.1169626266931032</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1531742650191734</v>
+        <v>0.01650000000000018</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -1620,108 +1632,108 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8631213392433116</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006492744915581773</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2907324908296564</v>
+        <v>0.8454437371166996</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01155213366104772</v>
+        <v>0.009700800200490399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5229396461150038</v>
+        <v>0.8608277232976554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006564777307101441</v>
+        <v>0.02216917078425409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2015338730293992</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01144868243932203</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8631 ± 0.0006</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.2907 ± 0.0116</t>
+          <t>0.8454 ± 0.0097</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.5229 ± 0.0066</t>
+          <t>0.8608 ± 0.0222</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.2015 ± 0.0114</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.8605687034984962</v>
+        <v>0.8445</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0001207060313439867</v>
+        <v>0.01802005056103403</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0003115709756448731</v>
+        <v>0.796119240811636</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0004643040521165739</v>
+        <v>0.008756581182760924</v>
       </c>
       <c r="R6" t="n">
-        <v>0.08583333333333334</v>
+        <v>0.758487229663299</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1153527199505933</v>
+        <v>0.01834829525959637</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001562278085499219</v>
+        <v>0.8445</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0002329387795321222</v>
+        <v>0.01802005056103403</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.8606 ± 0.0001</t>
+          <t>0.8445 ± 0.0180</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0003 ± 0.0005</t>
+          <t>0.7961 ± 0.0088</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.0858 ± 0.1154</t>
+          <t>0.7585 ± 0.0183</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0002 ± 0.0002</t>
+          <t>0.8445 ± 0.0180</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.002552635744815346</v>
+        <v>0.03300000000000003</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.2904209198540115</v>
+        <v>0.04932449630506364</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.4371063127816704</v>
+        <v>0.1023404936343565</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.2013776452208493</v>
+        <v>0.03300000000000003</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1732,108 +1744,108 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8585760645876208</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008837008421368494</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2542904020111528</v>
+        <v>0.835494258836275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004123268112439032</v>
+        <v>0.01145355069185408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4792228106524696</v>
+        <v>0.847039871734004</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0086336230115462</v>
+        <v>0.01822934405953743</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1730720068172134</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003012275509749968</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8586 ± 0.0009</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.2543 ± 0.0041</t>
+          <t>0.8355 ± 0.0115</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.4792 ± 0.0086</t>
+          <t>0.8470 ± 0.0182</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.1731 ± 0.0030</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.8585087858160518</v>
+        <v>0.8535</v>
       </c>
       <c r="O7" t="n">
-        <v>0.000923277687889107</v>
+        <v>0.01155902725626648</v>
       </c>
       <c r="P7" t="n">
-        <v>0.00294689508052617</v>
+        <v>0.7965978908265624</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.001366092119697046</v>
+        <v>0.005845409311343877</v>
       </c>
       <c r="R7" t="n">
-        <v>0.08194104491453391</v>
+        <v>0.7468518093699863</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01995972588599695</v>
+        <v>0.001392603248407127</v>
       </c>
       <c r="T7" t="n">
-        <v>0.001505467973299247</v>
+        <v>0.8535</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0007106942765628066</v>
+        <v>0.01155902725626648</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.8585 ± 0.0009</t>
+          <t>0.8535 ± 0.0116</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.0029 ± 0.0014</t>
+          <t>0.7966 ± 0.0058</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0819 ± 0.0200</t>
+          <t>0.7469 ± 0.0014</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.0015 ± 0.0007</t>
+          <t>0.8535 ± 0.0116</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>6.727877156897932e-05</v>
+        <v>0.01899999999999991</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.2513435069306267</v>
+        <v>0.03889636800971263</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3972817657379357</v>
+        <v>0.1001880623640177</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.1715665388439142</v>
+        <v>0.01899999999999991</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1844,108 +1856,108 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8577034193446256</v>
+        <v>0.8665</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001100478021426305</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2518109924417331</v>
+        <v>0.8492915770742749</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00902185699517897</v>
+        <v>0.01093808385599739</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4710247118621849</v>
+        <v>0.8431685063356953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01001864628250197</v>
+        <v>0.01341255506478664</v>
       </c>
       <c r="H8" t="n">
-        <v>0.171964209629314</v>
+        <v>0.8665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008237907025316163</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.8577 ± 0.0011</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.2518 ± 0.0090</t>
+          <t>0.8493 ± 0.0109</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.4710 ± 0.0100</t>
+          <t>0.8432 ± 0.0134</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.1720 ± 0.0082</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.7278692417286687</v>
+        <v>0.8324999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02918620347758178</v>
+        <v>0.01317615691736823</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1496721451029945</v>
+        <v>0.7879238545634504</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02576138707150587</v>
+        <v>0.007710276594733493</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1333702775690188</v>
+        <v>0.7495954822625809</v>
       </c>
       <c r="S8" t="n">
-        <v>0.018098328120112</v>
+        <v>0.01130598131083171</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1745916773185627</v>
+        <v>0.8324999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0448853839259956</v>
+        <v>0.01317615691736823</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.7279 ± 0.0292</t>
+          <t>0.8325 ± 0.0132</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.1497 ± 0.0258</t>
+          <t>0.7879 ± 0.0077</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.1334 ± 0.0181</t>
+          <t>0.7496 ± 0.0113</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.1746 ± 0.0449</t>
+          <t>0.8325 ± 0.0132</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0.1298341776159568</v>
+        <v>0.03400000000000014</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.1021388473387386</v>
+        <v>0.06136772251082456</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.3376544342931661</v>
+        <v>0.09357302407311441</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.00262746768924868</v>
+        <v>0.03400000000000014</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1956,108 +1968,108 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8513356814943801</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009037427725112313</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2488266547845204</v>
+        <v>0.8120777569572144</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00511286061119995</v>
+        <v>0.009746337201211541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4203678342656352</v>
+        <v>0.7948074615792644</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006991258369007768</v>
+        <v>0.01564230257413808</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1767504615821616</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00462847729159016</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.8513 ± 0.0009</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.2488 ± 0.0051</t>
+          <t>0.8121 ± 0.0097</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.4204 ± 0.0070</t>
+          <t>0.7948 ± 0.0156</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.1768 ± 0.0046</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.8518679753047333</v>
+        <v>0.8455</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001281820538095891</v>
+        <v>0.01039497741967513</v>
       </c>
       <c r="P9" t="n">
-        <v>0.01348859401639657</v>
+        <v>0.795035527912038</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.003660832807467163</v>
+        <v>0.008164230429254637</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0927921871297462</v>
+        <v>0.7569794205256127</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01738189120774628</v>
+        <v>0.01940062770836523</v>
       </c>
       <c r="T9" t="n">
-        <v>0.007285896889646357</v>
+        <v>0.8455</v>
       </c>
       <c r="U9" t="n">
-        <v>0.002043437308587493</v>
+        <v>0.01039497741967513</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.8519 ± 0.0013</t>
+          <t>0.8455 ± 0.0104</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.0135 ± 0.0037</t>
+          <t>0.7950 ± 0.0082</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.0928 ± 0.0174</t>
+          <t>0.7570 ± 0.0194</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.0073 ± 0.0020</t>
+          <t>0.8455 ± 0.0104</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>-0.000532293810353246</v>
+        <v>0.002999999999999892</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.2353380607681239</v>
+        <v>0.01704222904517638</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.327575647135889</v>
+        <v>0.03782804105365167</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.1694645646925153</v>
+        <v>0.002999999999999892</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -2068,108 +2080,108 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8472158461294919</v>
+        <v>0.794</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009310588989812209</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2760073032098657</v>
+        <v>0.7991552319401397</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003654438442907095</v>
+        <v>0.01874904662857105</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4062323582339051</v>
+        <v>0.806926929702948</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00489709142841155</v>
+        <v>0.01474411983059894</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2090470103678455</v>
+        <v>0.794</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004094394489595194</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8472 ± 0.0009</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.2760 ± 0.0037</t>
+          <t>0.7992 ± 0.0187</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.4062 ± 0.0049</t>
+          <t>0.8069 ± 0.0147</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.2090 ± 0.0041</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.8458029919265474</v>
+        <v>0.7595</v>
       </c>
       <c r="O10" t="n">
-        <v>0.001758857064936351</v>
+        <v>0.04969071006402169</v>
       </c>
       <c r="P10" t="n">
-        <v>0.02865520606143544</v>
+        <v>0.7579048370761177</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.004073347901818477</v>
+        <v>0.0287833643353949</v>
       </c>
       <c r="R10" t="n">
-        <v>0.1172782293793152</v>
+        <v>0.7580658653685093</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01220490747916881</v>
+        <v>0.01422434066153863</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01634710978554182</v>
+        <v>0.7595</v>
       </c>
       <c r="U10" t="n">
-        <v>0.002488848681350422</v>
+        <v>0.04969071006402169</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.8458 ± 0.0018</t>
+          <t>0.7595 ± 0.0497</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.0287 ± 0.0041</t>
+          <t>0.7579 ± 0.0288</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.1173 ± 0.0122</t>
+          <t>0.7581 ± 0.0142</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.0163 ± 0.0025</t>
+          <t>0.7595 ± 0.0497</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>0.001412854202944458</v>
+        <v>0.03450000000000009</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2473520971484303</v>
+        <v>0.04125039486402204</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.2889541288545898</v>
+        <v>0.04886106433443871</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1926999005823037</v>
+        <v>0.03450000000000009</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -2184,104 +2196,104 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7729420611049548</v>
+        <v>0.758</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001604092504916999</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4111314934218446</v>
+        <v>0.7695653113724968</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002269244542275589</v>
+        <v>0.1866093154578636</v>
       </c>
       <c r="F11" t="n">
-        <v>0.32188092350958</v>
+        <v>0.8530475252301031</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001866083751005921</v>
+        <v>0.01193960102018576</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5689106660985656</v>
+        <v>0.758</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005812999479801975</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.7729 ± 0.0016</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.4111 ± 0.0023</t>
+          <t>0.7696 ± 0.1866</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.3219 ± 0.0019</t>
+          <t>0.8530 ± 0.0119</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.5689 ± 0.0058</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.8468933037834414</v>
+        <v>0.7575000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>0.02330599669903018</v>
+        <v>0.01359125535858342</v>
       </c>
       <c r="P11" t="n">
-        <v>0.003204708991913499</v>
+        <v>0.7584484002038779</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.004453870499127896</v>
+        <v>0.005896346373562807</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2309094898784584</v>
+        <v>0.7597922138141208</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3871458237319818</v>
+        <v>0.005570077145047665</v>
       </c>
       <c r="T11" t="n">
-        <v>0.002130379207498935</v>
+        <v>0.7575000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>0.003106427635731815</v>
+        <v>0.01359125535858342</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.8469 ± 0.0233</t>
+          <t>0.7575 ± 0.0136</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.0032 ± 0.0045</t>
+          <t>0.7584 ± 0.0059</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.2309 ± 0.3871</t>
+          <t>0.7598 ± 0.0056</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0021 ± 0.0031</t>
+          <t>0.7575 ± 0.0136</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>-0.07395124267848663</v>
+        <v>0.0004999999999999449</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.4079267844299311</v>
+        <v>0.0111169111686189</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.09097143363112159</v>
+        <v>0.09325531141598231</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.5667802868910666</v>
+        <v>0.0004999999999999449</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2304,152 +2316,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -2458,108 +2470,108 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8653850720278614</v>
+        <v>0.8965</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0004897208981754782</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1722933021134507</v>
+        <v>0.8800945612919768</v>
       </c>
       <c r="E2" t="n">
-        <v>0.004133046767167164</v>
+        <v>0.01557076241163555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6012194836101217</v>
+        <v>0.8849723263768654</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01161315896115709</v>
+        <v>0.01637849998720951</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1005681011219997</v>
+        <v>0.8965</v>
       </c>
       <c r="I2" t="n">
-        <v>0.002743294672201886</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.8654 ± 0.0005</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.1723 ± 0.0041</t>
+          <t>0.8801 ± 0.0156</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.6012 ± 0.0116</t>
+          <t>0.8850 ± 0.0164</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.1006 ± 0.0027</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.8594328795314231</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.001759943124097367</v>
+        <v>0.008644201653259968</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2332054266594181</v>
+        <v>0.8740589613153219</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02311148836982272</v>
+        <v>0.008504514563610215</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4856082623037368</v>
+        <v>0.8717974753920386</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01937159125545948</v>
+        <v>0.009961185756881206</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1538985939497231</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01868074662662275</v>
+        <v>0.008644201653259968</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.8594 ± 0.0018</t>
+          <t>0.8845 ± 0.0086</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.2332 ± 0.0231</t>
+          <t>0.8741 ± 0.0085</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.4856 ± 0.0194</t>
+          <t>0.8718 ± 0.0100</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.1539 ± 0.0187</t>
+          <t>0.8845 ± 0.0086</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>0.005952192496438302</v>
+        <v>0.0119999999999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>-0.06091212454596739</v>
+        <v>0.006035599976654926</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.1156112213063848</v>
+        <v>0.01317485098482685</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.05333049282772336</v>
+        <v>0.0119999999999999</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -2570,108 +2582,108 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8644649358872882</v>
+        <v>0.8905</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001292019377334109</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2639376061713777</v>
+        <v>0.8613575595536576</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0296521977876718</v>
+        <v>0.00835629357808527</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5445815044621426</v>
+        <v>0.8875770769739587</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01990884968502404</v>
+        <v>0.009319454743331457</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1754864365857122</v>
+        <v>0.8905</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02609605447626427</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.8645 ± 0.0013</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.2639 ± 0.0297</t>
+          <t>0.8614 ± 0.0084</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.5446 ± 0.0199</t>
+          <t>0.8876 ± 0.0093</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.1755 ± 0.0261</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.8458979737217034</v>
+        <v>0.892</v>
       </c>
       <c r="O3" t="n">
-        <v>0.002917769493011457</v>
+        <v>0.007527726527090817</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2957141512829655</v>
+        <v>0.8748453500252168</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01191860841862675</v>
+        <v>0.007458169753921906</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4073866373875522</v>
+        <v>0.8792862472502394</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01658665615007694</v>
+        <v>0.01186372439962882</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2322965487856838</v>
+        <v>0.892</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01168656640890678</v>
+        <v>0.007527726527090817</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.8459 ± 0.0029</t>
+          <t>0.8920 ± 0.0075</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.2957 ± 0.0119</t>
+          <t>0.8748 ± 0.0075</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4074 ± 0.0166</t>
+          <t>0.8793 ± 0.0119</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.2323 ± 0.0117</t>
+          <t>0.8920 ± 0.0075</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>0.01856696216558484</v>
+        <v>-0.001500000000000057</v>
       </c>
       <c r="AA3" t="n">
-        <v>-0.03177654511158778</v>
+        <v>-0.01348779047155924</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.1371948670745904</v>
+        <v>0.008290829723719306</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.05681011219997162</v>
+        <v>-0.001500000000000057</v>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
@@ -2686,104 +2698,104 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8635903118568941</v>
+        <v>0.8815</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003809564049741432</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="D4" t="n">
-        <v>0.121804936464582</v>
+        <v>0.8395197032079371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00369981836688605</v>
+        <v>0.007183950573405901</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.8927447421022293</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01145382697210849</v>
+        <v>0.01169636211175201</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06790228660701605</v>
+        <v>0.8815</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002191473549437678</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.8636 ± 0.0004</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.1218 ± 0.0037</t>
+          <t>0.8395 ± 0.0072</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5911 ± 0.0115</t>
+          <t>0.8927 ± 0.0117</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.0679 ± 0.0022</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.8604875732151337</v>
+        <v>0.89</v>
       </c>
       <c r="O4" t="n">
-        <v>0.001281887740118282</v>
+        <v>0.006236095644623242</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1989911005639252</v>
+        <v>0.8622741608593515</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01500809222967246</v>
+        <v>0.0107043530784709</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4982550661193003</v>
+        <v>0.8831176570216487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0187804029255209</v>
+        <v>0.01004847749414569</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1246129811106377</v>
+        <v>0.89</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01208270422522765</v>
+        <v>0.006236095644623242</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.8605 ± 0.0013</t>
+          <t>0.8900 ± 0.0062</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.1990 ± 0.0150</t>
+          <t>0.8623 ± 0.0107</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.4983 ± 0.0188</t>
+          <t>0.8831 ± 0.0100</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.1246 ± 0.0121</t>
+          <t>0.8900 ± 0.0062</t>
         </is>
       </c>
       <c r="Z4" t="n">
-        <v>0.003102738641760361</v>
+        <v>-0.008500000000000063</v>
       </c>
       <c r="AA4" t="n">
-        <v>-0.07718616409934326</v>
+        <v>-0.02275445765141437</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0928409769750092</v>
+        <v>0.009627085080580633</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.05671069450362165</v>
+        <v>-0.008500000000000063</v>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
@@ -2794,108 +2806,108 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8635467785341143</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0007481700690606898</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2388691165223189</v>
+        <v>0.8460496521431005</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004564487931064464</v>
+        <v>0.01294479429530151</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5359686608772588</v>
+        <v>0.865010991243126</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00934558839892455</v>
+        <v>0.02161817607890089</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1536855560289732</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003128072545874311</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.8635 ± 0.0007</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.2389 ± 0.0046</t>
+          <t>0.8460 ± 0.0129</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.5360 ± 0.0093</t>
+          <t>0.8650 ± 0.0216</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.1537 ± 0.0031</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.856987098306158</v>
+        <v>0.867</v>
       </c>
       <c r="O5" t="n">
-        <v>0.001738656117874269</v>
+        <v>0.008232726023485654</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2715592523047302</v>
+        <v>0.8317730476364493</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01050519745940829</v>
+        <v>0.009232178771023704</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4680979723508488</v>
+        <v>0.8361931687425281</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01428075603395597</v>
+        <v>0.02217992328586535</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1914642806419543</v>
+        <v>0.867</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01030959740478241</v>
+        <v>0.008232726023485654</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.8570 ± 0.0017</t>
+          <t>0.8670 ± 0.0082</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2716 ± 0.0105</t>
+          <t>0.8318 ± 0.0092</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.4681 ± 0.0143</t>
+          <t>0.8362 ± 0.0222</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.1915 ± 0.0103</t>
+          <t>0.8670 ± 0.0082</t>
         </is>
       </c>
       <c r="Z5" t="n">
-        <v>0.006559680227956277</v>
+        <v>0.01300000000000012</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.03269013578241131</v>
+        <v>0.01427660450665114</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.06787068852641004</v>
+        <v>0.02881782250059783</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.0377787246129811</v>
+        <v>0.01300000000000012</v>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
@@ -2906,108 +2918,108 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8631213392433116</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0006492744915581773</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2907324908296564</v>
+        <v>0.8454437371166996</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01155213366104772</v>
+        <v>0.009700800200490399</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5229396461150038</v>
+        <v>0.8608277232976554</v>
       </c>
       <c r="G6" t="n">
-        <v>0.006564777307101441</v>
+        <v>0.02216917078425409</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2015338730293992</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01144868243932203</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.8631 ± 0.0006</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.2907 ± 0.0116</t>
+          <t>0.8454 ± 0.0097</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.5229 ± 0.0066</t>
+          <t>0.8608 ± 0.0222</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.2015 ± 0.0114</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.852685214500554</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>0.004990014161301725</v>
+        <v>0.01173787790777268</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3054179008255341</v>
+        <v>0.8356806037864141</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04469072687172702</v>
+        <v>0.01296409706277128</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4471802147018231</v>
+        <v>0.8278647307416687</v>
       </c>
       <c r="S6" t="n">
-        <v>0.03475350145014876</v>
+        <v>0.01624445982897337</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2357619656298821</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.05021098864555093</v>
+        <v>0.01173787790777268</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0.8527 ± 0.0050</t>
+          <t>0.8560 ± 0.0117</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.3054 ± 0.0447</t>
+          <t>0.8357 ± 0.0130</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0.4472 ± 0.0348</t>
+          <t>0.8279 ± 0.0162</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.2358 ± 0.0502</t>
+          <t>0.8560 ± 0.0117</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>0.01043612474275757</v>
+        <v>0.02149999999999996</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.0146854099958777</v>
+        <v>0.009763133330285556</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0757594314131807</v>
+        <v>0.03296299255598678</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.03422809260048287</v>
+        <v>0.02149999999999996</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -3018,108 +3030,108 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8585760645876208</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008837008421368494</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2542904020111528</v>
+        <v>0.835494258836275</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004123268112439032</v>
+        <v>0.01145355069185408</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4792228106524696</v>
+        <v>0.847039871734004</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0086336230115462</v>
+        <v>0.01822934405953743</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1730720068172134</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.003012275509749968</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.8586 ± 0.0009</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.2543 ± 0.0041</t>
+          <t>0.8355 ± 0.0115</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.4792 ± 0.0086</t>
+          <t>0.8470 ± 0.0182</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.1731 ± 0.0030</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.8582060313439925</v>
+        <v>0.8725000000000002</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0009257278421097861</v>
+        <v>0.0088975652100261</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2026390078200694</v>
+        <v>0.8390546705140765</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01406088839275979</v>
+        <v>0.01296203029878578</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4680956246527622</v>
+        <v>0.8446664360507107</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01129415337352562</v>
+        <v>0.01936142229675867</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1295128532878853</v>
+        <v>0.8725000000000002</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01107295433695692</v>
+        <v>0.0088975652100261</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>0.8582 ± 0.0009</t>
+          <t>0.8725 ± 0.0089</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2026 ± 0.0141</t>
+          <t>0.8391 ± 0.0130</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.4681 ± 0.0113</t>
+          <t>0.8447 ± 0.0194</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.1295 ± 0.0111</t>
+          <t>0.8725 ± 0.0089</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003700332436282761</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.05165139419108342</v>
+        <v>-0.003560411677801412</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.01112718599970741</v>
+        <v>0.00237343568329329</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.04355915352932818</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -3130,108 +3142,108 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8577034193446256</v>
+        <v>0.8665</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001100478021426305</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2518109924417331</v>
+        <v>0.8492915770742749</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00902185699517897</v>
+        <v>0.01093808385599739</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4710247118621849</v>
+        <v>0.8431685063356953</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01001864628250197</v>
+        <v>0.01341255506478664</v>
       </c>
       <c r="H8" t="n">
-        <v>0.171964209629314</v>
+        <v>0.8665</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008237907025316163</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.8577 ± 0.0011</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.2518 ± 0.0090</t>
+          <t>0.8493 ± 0.0109</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.4710 ± 0.0100</t>
+          <t>0.8432 ± 0.0134</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.1720 ± 0.0082</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.7933453379768878</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008179284861907412</v>
+        <v>0.01370320319406299</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3083582846944011</v>
+        <v>0.8513079585760513</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01201275374419538</v>
+        <v>0.01472495814796158</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2895576392844975</v>
+        <v>0.8452658116236673</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008417614778537561</v>
+        <v>0.01704866229207197</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3313733844624343</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.02846916497887783</v>
+        <v>0.01370320319406299</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.7933 ± 0.0082</t>
+          <t>0.8640 ± 0.0137</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.3084 ± 0.0120</t>
+          <t>0.8513 ± 0.0147</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.2896 ± 0.0084</t>
+          <t>0.8453 ± 0.0170</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.3314 ± 0.0285</t>
+          <t>0.8640 ± 0.0137</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>0.0643580813677378</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="AA8" t="n">
-        <v>-0.05654729225266808</v>
+        <v>-0.00201638150177641</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.1814670725776874</v>
+        <v>-0.002097305287972029</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1594091748331203</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -3242,108 +3254,108 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8513356814943801</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009037427725112313</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2488266547845204</v>
+        <v>0.8120777569572144</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00511286061119995</v>
+        <v>0.009746337201211541</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4203678342656352</v>
+        <v>0.7948074615792644</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006991258369007768</v>
+        <v>0.01564230257413808</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1767504615821616</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00462847729159016</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.8513 ± 0.0009</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.2488 ± 0.0051</t>
+          <t>0.8121 ± 0.0097</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.4204 ± 0.0070</t>
+          <t>0.7948 ± 0.0156</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.1768 ± 0.0046</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.8530750356181732</v>
+        <v>0.8644999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.001212077950855918</v>
+        <v>0.005986094998689329</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1982972877374191</v>
+        <v>0.8397690328049215</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01733491557879429</v>
+        <v>0.008733820353619547</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4129480942886304</v>
+        <v>0.8344313125015056</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01702310751314772</v>
+        <v>0.01128806302708654</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1306632580599347</v>
+        <v>0.8644999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01363324333261546</v>
+        <v>0.005986094998689329</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.8531 ± 0.0012</t>
+          <t>0.8645 ± 0.0060</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.1983 ± 0.0173</t>
+          <t>0.8398 ± 0.0087</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.4129 ± 0.0170</t>
+          <t>0.8344 ± 0.0113</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.1307 ± 0.0136</t>
+          <t>0.8645 ± 0.0060</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>-0.001739354123793113</v>
+        <v>-0.01600000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.05052936704710131</v>
+        <v>-0.02769127584770714</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.007419739977004791</v>
+        <v>-0.03962385092224119</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.04608720352222695</v>
+        <v>-0.01600000000000001</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -3354,108 +3366,108 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8472158461294919</v>
+        <v>0.794</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0009310588989812209</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2760073032098657</v>
+        <v>0.7991552319401397</v>
       </c>
       <c r="E10" t="n">
-        <v>0.003654438442907095</v>
+        <v>0.01874904662857105</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4062323582339051</v>
+        <v>0.806926929702948</v>
       </c>
       <c r="G10" t="n">
-        <v>0.00489709142841155</v>
+        <v>0.01474411983059894</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2090470103678455</v>
+        <v>0.794</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004094394489595194</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.8472 ± 0.0009</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.2760 ± 0.0037</t>
+          <t>0.7992 ± 0.0187</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.4062 ± 0.0049</t>
+          <t>0.8069 ± 0.0147</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.2090 ± 0.0041</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.8443703498496122</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.002155324629646412</v>
+        <v>0.02608213522274928</v>
       </c>
       <c r="P10" t="n">
-        <v>0.231243963132944</v>
+        <v>0.7869109458280485</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0137006705544126</v>
+        <v>0.02195959925702665</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3707827247491188</v>
+        <v>0.81003273111726</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01709342485110321</v>
+        <v>0.0191996780030147</v>
       </c>
       <c r="T10" t="n">
-        <v>0.168115324527766</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01152280256385812</v>
+        <v>0.02608213522274928</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.8444 ± 0.0022</t>
+          <t>0.7695 ± 0.0261</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.2312 ± 0.0137</t>
+          <t>0.7869 ± 0.0220</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.3708 ± 0.0171</t>
+          <t>0.8100 ± 0.0192</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.1681 ± 0.0115</t>
+          <t>0.7695 ± 0.0261</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>0.002845496279879622</v>
+        <v>0.02449999999999997</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.04476334007692173</v>
+        <v>0.01224428611209116</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.03544963348478625</v>
+        <v>-0.003105801414312048</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.04093168584007956</v>
+        <v>0.02449999999999997</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -3470,104 +3482,104 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7729420611049548</v>
+        <v>0.758</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001604092504916999</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4111314934218446</v>
+        <v>0.7695653113724968</v>
       </c>
       <c r="E11" t="n">
-        <v>0.002269244542275589</v>
+        <v>0.1866093154578636</v>
       </c>
       <c r="F11" t="n">
-        <v>0.32188092350958</v>
+        <v>0.8530475252301031</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001866083751005921</v>
+        <v>0.01193960102018576</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5689106660985656</v>
+        <v>0.758</v>
       </c>
       <c r="I11" t="n">
-        <v>0.005812999479801975</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.7729 ± 0.0016</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.4111 ± 0.0023</t>
+          <t>0.7696 ± 0.1866</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.3219 ± 0.0019</t>
+          <t>0.8530 ± 0.0119</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.5689 ± 0.0058</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.2876800696533165</v>
+        <v>0.5515</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01325794881831392</v>
+        <v>0.2603528588495066</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2721032847164263</v>
+        <v>0.5707855242882436</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.003645391628123934</v>
+        <v>0.2617419349196998</v>
       </c>
       <c r="R11" t="n">
-        <v>0.1586495092299866</v>
+        <v>0.864237257200078</v>
       </c>
       <c r="S11" t="n">
-        <v>0.002465782440245203</v>
+        <v>0.01629017285189378</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9553756568669224</v>
+        <v>0.5515</v>
       </c>
       <c r="U11" t="n">
-        <v>0.005611274864304836</v>
+        <v>0.2603528588495066</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.2877 ± 0.0133</t>
+          <t>0.5515 ± 0.2604</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.2721 ± 0.0036</t>
+          <t>0.5708 ± 0.2617</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.1586 ± 0.0025</t>
+          <t>0.8642 ± 0.0163</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.9554 ± 0.0056</t>
+          <t>0.5515 ± 0.2604</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>0.4852619914516383</v>
+        <v>0.2065</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.1390282087054183</v>
+        <v>0.1987797870842533</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.1632314142795934</v>
+        <v>-0.01118973196997497</v>
       </c>
       <c r="AC11" t="n">
-        <v>-0.3864649907683568</v>
+        <v>0.2065</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -3590,152 +3602,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -10464,224 +10476,224 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8653850720278614</v>
+        <v>0.8965</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0004897208981754782</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="D62" t="n">
-        <v>0.1722933021134507</v>
+        <v>0.8800945612919768</v>
       </c>
       <c r="E62" t="n">
-        <v>0.004133046767167164</v>
+        <v>0.01557076241163555</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6012194836101217</v>
+        <v>0.8849723263768654</v>
       </c>
       <c r="G62" t="n">
-        <v>0.01161315896115709</v>
+        <v>0.01637849998720951</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1005681011219997</v>
+        <v>0.8965</v>
       </c>
       <c r="I62" t="n">
-        <v>0.002743294672201886</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>0.8654 ± 0.0005</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>0.1723 ± 0.0041</t>
+          <t>0.8801 ± 0.0156</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0.6012 ± 0.0116</t>
+          <t>0.8850 ± 0.0164</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>0.1006 ± 0.0027</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.8594328795314231</v>
+        <v>0.865</v>
       </c>
       <c r="O62" t="n">
-        <v>0.001759943124097367</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>0.2332054266594181</v>
+        <v>0.8023860589812333</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.02311148836982272</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>0.4856082623037368</v>
+        <v>0.7482249999999999</v>
       </c>
       <c r="S62" t="n">
-        <v>0.01937159125545948</v>
+        <v>1.1702778228589e-16</v>
       </c>
       <c r="T62" t="n">
-        <v>0.1538985939497231</v>
+        <v>0.865</v>
       </c>
       <c r="U62" t="n">
-        <v>0.01868074662662275</v>
+        <v>0</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>0.8594 ± 0.0018</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>0.2332 ± 0.0231</t>
+          <t>0.8024 ± 0.0000</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>0.4856 ± 0.0194</t>
+          <t>0.7482 ± 0.0000</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>0.1539 ± 0.0187</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="Z62" t="n">
-        <v>0.005952192496438302</v>
+        <v>0.03149999999999997</v>
       </c>
       <c r="AA62" t="n">
-        <v>-0.06091212454596739</v>
+        <v>0.07770850231074355</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.1156112213063848</v>
+        <v>0.1367473263768655</v>
       </c>
       <c r="AC62" t="n">
-        <v>-0.05333049282772336</v>
+        <v>0.03149999999999997</v>
       </c>
       <c r="AD62" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8644649358872882</v>
+        <v>0.8905</v>
       </c>
       <c r="C63" t="n">
-        <v>0.001292019377334109</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="D63" t="n">
-        <v>0.2639376061713777</v>
+        <v>0.8613575595536576</v>
       </c>
       <c r="E63" t="n">
-        <v>0.0296521977876718</v>
+        <v>0.00835629357808527</v>
       </c>
       <c r="F63" t="n">
-        <v>0.5445815044621426</v>
+        <v>0.8875770769739587</v>
       </c>
       <c r="G63" t="n">
-        <v>0.01990884968502404</v>
+        <v>0.009319454743331457</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1754864365857122</v>
+        <v>0.8905</v>
       </c>
       <c r="I63" t="n">
-        <v>0.02609605447626427</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>0.8645 ± 0.0013</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>0.2639 ± 0.0297</t>
+          <t>0.8614 ± 0.0084</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>0.5446 ± 0.0199</t>
+          <t>0.8876 ± 0.0093</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>0.1755 ± 0.0261</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0.8458979737217034</v>
+        <v>0.8625</v>
       </c>
       <c r="O63" t="n">
-        <v>0.002917769493011457</v>
+        <v>0.003535533905932741</v>
       </c>
       <c r="P63" t="n">
-        <v>0.2957141512829655</v>
+        <v>0.8011379217986173</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.01191860841862675</v>
+        <v>0.001766402176797399</v>
       </c>
       <c r="R63" t="n">
-        <v>0.4073866373875522</v>
+        <v>0.7479310027409777</v>
       </c>
       <c r="S63" t="n">
-        <v>0.01658665615007694</v>
+        <v>0.0004163356235445011</v>
       </c>
       <c r="T63" t="n">
-        <v>0.2322965487856838</v>
+        <v>0.8625</v>
       </c>
       <c r="U63" t="n">
-        <v>0.01168656640890678</v>
+        <v>0.003535533905932741</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>0.8459 ± 0.0029</t>
+          <t>0.8625 ± 0.0035</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>0.2957 ± 0.0119</t>
+          <t>0.8011 ± 0.0018</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>0.4074 ± 0.0166</t>
+          <t>0.7479 ± 0.0004</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>0.2323 ± 0.0117</t>
+          <t>0.8625 ± 0.0035</t>
         </is>
       </c>
       <c r="Z63" t="n">
-        <v>0.01856696216558484</v>
+        <v>0.02799999999999991</v>
       </c>
       <c r="AA63" t="n">
-        <v>-0.03177654511158778</v>
+        <v>0.06021963775504025</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.1371948670745904</v>
+        <v>0.139646074232981</v>
       </c>
       <c r="AC63" t="n">
-        <v>-0.05681011219997162</v>
+        <v>0.02799999999999991</v>
       </c>
       <c r="AD63" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -10692,780 +10704,780 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8635903118568941</v>
+        <v>0.8815</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0003809564049741432</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="D64" t="n">
-        <v>0.121804936464582</v>
+        <v>0.8395197032079371</v>
       </c>
       <c r="E64" t="n">
-        <v>0.00369981836688605</v>
+        <v>0.007183950573405901</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.8927447421022293</v>
       </c>
       <c r="G64" t="n">
-        <v>0.01145382697210849</v>
+        <v>0.01169636211175201</v>
       </c>
       <c r="H64" t="n">
-        <v>0.06790228660701605</v>
+        <v>0.8815</v>
       </c>
       <c r="I64" t="n">
-        <v>0.002191473549437678</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>0.8636 ± 0.0004</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>0.1218 ± 0.0037</t>
+          <t>0.8395 ± 0.0072</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>0.5911 ± 0.0115</t>
+          <t>0.8927 ± 0.0117</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>0.0679 ± 0.0022</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0.8604875732151337</v>
+        <v>0.865</v>
       </c>
       <c r="O64" t="n">
-        <v>0.001281887740118282</v>
+        <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>0.1989911005639252</v>
+        <v>0.8023860589812333</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.01500809222967246</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>0.4982550661193003</v>
+        <v>0.7482249999999999</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0187804029255209</v>
+        <v>1.1702778228589e-16</v>
       </c>
       <c r="T64" t="n">
-        <v>0.1246129811106377</v>
+        <v>0.865</v>
       </c>
       <c r="U64" t="n">
-        <v>0.01208270422522765</v>
+        <v>0</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>0.8605 ± 0.0013</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>0.1990 ± 0.0150</t>
+          <t>0.8024 ± 0.0000</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>0.4983 ± 0.0188</t>
+          <t>0.7482 ± 0.0000</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>0.1246 ± 0.0121</t>
+          <t>0.8650 ± 0.0000</t>
         </is>
       </c>
       <c r="Z64" t="n">
-        <v>0.003102738641760361</v>
+        <v>0.01649999999999996</v>
       </c>
       <c r="AA64" t="n">
-        <v>-0.07718616409934326</v>
+        <v>0.03713364422670384</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.0928409769750092</v>
+        <v>0.1445197421022294</v>
       </c>
       <c r="AC64" t="n">
-        <v>-0.05671069450362165</v>
+        <v>0.01649999999999996</v>
       </c>
       <c r="AD64" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8635467785341143</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0007481700690606898</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="D65" t="n">
-        <v>0.2388691165223189</v>
+        <v>0.8460496521431005</v>
       </c>
       <c r="E65" t="n">
-        <v>0.004564487931064464</v>
+        <v>0.01294479429530151</v>
       </c>
       <c r="F65" t="n">
-        <v>0.5359686608772588</v>
+        <v>0.865010991243126</v>
       </c>
       <c r="G65" t="n">
-        <v>0.00934558839892455</v>
+        <v>0.02161817607890089</v>
       </c>
       <c r="H65" t="n">
-        <v>0.1536855560289732</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>0.003128072545874311</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>0.8635 ± 0.0007</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>0.2389 ± 0.0046</t>
+          <t>0.8460 ± 0.0129</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>0.5360 ± 0.0093</t>
+          <t>0.8650 ± 0.0216</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>0.1537 ± 0.0031</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.856987098306158</v>
+        <v>0.8634999999999999</v>
       </c>
       <c r="O65" t="n">
-        <v>0.001738656117874269</v>
+        <v>0.003374742788552767</v>
       </c>
       <c r="P65" t="n">
-        <v>0.2715592523047302</v>
+        <v>0.8016366389712081</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.01050519745940829</v>
+        <v>0.001686805320122046</v>
       </c>
       <c r="R65" t="n">
-        <v>0.4680979723508488</v>
+        <v>0.7480483645500228</v>
       </c>
       <c r="S65" t="n">
-        <v>0.01428075603395597</v>
+        <v>0.0003977256889716439</v>
       </c>
       <c r="T65" t="n">
-        <v>0.1914642806419543</v>
+        <v>0.8634999999999999</v>
       </c>
       <c r="U65" t="n">
-        <v>0.01030959740478241</v>
+        <v>0.003374742788552767</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>0.8570 ± 0.0017</t>
+          <t>0.8635 ± 0.0034</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>0.2716 ± 0.0105</t>
+          <t>0.8016 ± 0.0017</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>0.4681 ± 0.0143</t>
+          <t>0.7480 ± 0.0004</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>0.1915 ± 0.0103</t>
+          <t>0.8635 ± 0.0034</t>
         </is>
       </c>
       <c r="Z65" t="n">
-        <v>0.006559680227956277</v>
+        <v>0.01650000000000018</v>
       </c>
       <c r="AA65" t="n">
-        <v>-0.03269013578241131</v>
+        <v>0.04441301317189239</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.06787068852641004</v>
+        <v>0.1169626266931032</v>
       </c>
       <c r="AC65" t="n">
-        <v>-0.0377787246129811</v>
+        <v>0.01650000000000018</v>
       </c>
       <c r="AD65" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8631213392433116</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0006492744915581773</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="D66" t="n">
-        <v>0.2907324908296564</v>
+        <v>0.8454437371166996</v>
       </c>
       <c r="E66" t="n">
-        <v>0.01155213366104772</v>
+        <v>0.009700800200490399</v>
       </c>
       <c r="F66" t="n">
-        <v>0.5229396461150038</v>
+        <v>0.8608277232976554</v>
       </c>
       <c r="G66" t="n">
-        <v>0.006564777307101441</v>
+        <v>0.02216917078425409</v>
       </c>
       <c r="H66" t="n">
-        <v>0.2015338730293992</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>0.01144868243932203</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>0.8631 ± 0.0006</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>0.2907 ± 0.0116</t>
+          <t>0.8454 ± 0.0097</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>0.5229 ± 0.0066</t>
+          <t>0.8608 ± 0.0222</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>0.2015 ± 0.0114</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0.852685214500554</v>
+        <v>0.8445</v>
       </c>
       <c r="O66" t="n">
-        <v>0.004990014161301725</v>
+        <v>0.01802005056103403</v>
       </c>
       <c r="P66" t="n">
-        <v>0.3054179008255341</v>
+        <v>0.796119240811636</v>
       </c>
       <c r="Q66" t="n">
-        <v>0.04469072687172702</v>
+        <v>0.008756581182760924</v>
       </c>
       <c r="R66" t="n">
-        <v>0.4471802147018231</v>
+        <v>0.758487229663299</v>
       </c>
       <c r="S66" t="n">
-        <v>0.03475350145014876</v>
+        <v>0.01834829525959637</v>
       </c>
       <c r="T66" t="n">
-        <v>0.2357619656298821</v>
+        <v>0.8445</v>
       </c>
       <c r="U66" t="n">
-        <v>0.05021098864555093</v>
+        <v>0.01802005056103403</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>0.8527 ± 0.0050</t>
+          <t>0.8445 ± 0.0180</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>0.3054 ± 0.0447</t>
+          <t>0.7961 ± 0.0088</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>0.4472 ± 0.0348</t>
+          <t>0.7585 ± 0.0183</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>0.2358 ± 0.0502</t>
+          <t>0.8445 ± 0.0180</t>
         </is>
       </c>
       <c r="Z66" t="n">
-        <v>0.01043612474275757</v>
+        <v>0.03300000000000003</v>
       </c>
       <c r="AA66" t="n">
-        <v>-0.0146854099958777</v>
+        <v>0.04932449630506364</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.0757594314131807</v>
+        <v>0.1023404936343565</v>
       </c>
       <c r="AC66" t="n">
-        <v>-0.03422809260048287</v>
+        <v>0.03300000000000003</v>
       </c>
       <c r="AD66" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8585760645876208</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0008837008421368494</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="D67" t="n">
-        <v>0.2542904020111528</v>
+        <v>0.835494258836275</v>
       </c>
       <c r="E67" t="n">
-        <v>0.004123268112439032</v>
+        <v>0.01145355069185408</v>
       </c>
       <c r="F67" t="n">
-        <v>0.4792228106524696</v>
+        <v>0.847039871734004</v>
       </c>
       <c r="G67" t="n">
-        <v>0.0086336230115462</v>
+        <v>0.01822934405953743</v>
       </c>
       <c r="H67" t="n">
-        <v>0.1730720068172134</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>0.003012275509749968</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>0.8586 ± 0.0009</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>0.2543 ± 0.0041</t>
+          <t>0.8355 ± 0.0115</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>0.4792 ± 0.0086</t>
+          <t>0.8470 ± 0.0182</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>0.1731 ± 0.0030</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0.8582060313439925</v>
+        <v>0.8535</v>
       </c>
       <c r="O67" t="n">
-        <v>0.0009257278421097861</v>
+        <v>0.01155902725626648</v>
       </c>
       <c r="P67" t="n">
-        <v>0.2026390078200694</v>
+        <v>0.7965978908265624</v>
       </c>
       <c r="Q67" t="n">
-        <v>0.01406088839275979</v>
+        <v>0.005845409311343877</v>
       </c>
       <c r="R67" t="n">
-        <v>0.4680956246527622</v>
+        <v>0.7468518093699863</v>
       </c>
       <c r="S67" t="n">
-        <v>0.01129415337352562</v>
+        <v>0.001392603248407127</v>
       </c>
       <c r="T67" t="n">
-        <v>0.1295128532878853</v>
+        <v>0.8535</v>
       </c>
       <c r="U67" t="n">
-        <v>0.01107295433695692</v>
+        <v>0.01155902725626648</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>0.8582 ± 0.0009</t>
+          <t>0.8535 ± 0.0116</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>0.2026 ± 0.0141</t>
+          <t>0.7966 ± 0.0058</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>0.4681 ± 0.0113</t>
+          <t>0.7469 ± 0.0014</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>0.1295 ± 0.0111</t>
+          <t>0.8535 ± 0.0116</t>
         </is>
       </c>
       <c r="Z67" t="n">
-        <v>0.0003700332436282761</v>
+        <v>0.01899999999999991</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.05165139419108342</v>
+        <v>0.03889636800971263</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.01112718599970741</v>
+        <v>0.1001880623640177</v>
       </c>
       <c r="AC67" t="n">
-        <v>0.04355915352932818</v>
+        <v>0.01899999999999991</v>
       </c>
       <c r="AD67" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8577034193446256</v>
+        <v>0.8665</v>
       </c>
       <c r="C68" t="n">
-        <v>0.001100478021426305</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2518109924417331</v>
+        <v>0.8492915770742749</v>
       </c>
       <c r="E68" t="n">
-        <v>0.00902185699517897</v>
+        <v>0.01093808385599739</v>
       </c>
       <c r="F68" t="n">
-        <v>0.4710247118621849</v>
+        <v>0.8431685063356953</v>
       </c>
       <c r="G68" t="n">
-        <v>0.01001864628250197</v>
+        <v>0.01341255506478664</v>
       </c>
       <c r="H68" t="n">
-        <v>0.171964209629314</v>
+        <v>0.8665</v>
       </c>
       <c r="I68" t="n">
-        <v>0.008237907025316163</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>0.8577 ± 0.0011</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>0.2518 ± 0.0090</t>
+          <t>0.8493 ± 0.0109</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>0.4710 ± 0.0100</t>
+          <t>0.8432 ± 0.0134</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>0.1720 ± 0.0082</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0.7933453379768878</v>
+        <v>0.8324999999999999</v>
       </c>
       <c r="O68" t="n">
-        <v>0.008179284861907412</v>
+        <v>0.01317615691736823</v>
       </c>
       <c r="P68" t="n">
-        <v>0.3083582846944011</v>
+        <v>0.7879238545634504</v>
       </c>
       <c r="Q68" t="n">
-        <v>0.01201275374419538</v>
+        <v>0.007710276594733493</v>
       </c>
       <c r="R68" t="n">
-        <v>0.2895576392844975</v>
+        <v>0.7495954822625809</v>
       </c>
       <c r="S68" t="n">
-        <v>0.008417614778537561</v>
+        <v>0.01130598131083171</v>
       </c>
       <c r="T68" t="n">
-        <v>0.3313733844624343</v>
+        <v>0.8324999999999999</v>
       </c>
       <c r="U68" t="n">
-        <v>0.02846916497887783</v>
+        <v>0.01317615691736823</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>0.7933 ± 0.0082</t>
+          <t>0.8325 ± 0.0132</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>0.3084 ± 0.0120</t>
+          <t>0.7879 ± 0.0077</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>0.2896 ± 0.0084</t>
+          <t>0.7496 ± 0.0113</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>0.3314 ± 0.0285</t>
+          <t>0.8325 ± 0.0132</t>
         </is>
       </c>
       <c r="Z68" t="n">
-        <v>0.0643580813677378</v>
+        <v>0.03400000000000014</v>
       </c>
       <c r="AA68" t="n">
-        <v>-0.05654729225266808</v>
+        <v>0.06136772251082456</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.1814670725776874</v>
+        <v>0.09357302407311441</v>
       </c>
       <c r="AC68" t="n">
-        <v>-0.1594091748331203</v>
+        <v>0.03400000000000014</v>
       </c>
       <c r="AD68" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8513356814943801</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0009037427725112313</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="D69" t="n">
-        <v>0.2488266547845204</v>
+        <v>0.8120777569572144</v>
       </c>
       <c r="E69" t="n">
-        <v>0.00511286061119995</v>
+        <v>0.009746337201211541</v>
       </c>
       <c r="F69" t="n">
-        <v>0.4203678342656352</v>
+        <v>0.7948074615792644</v>
       </c>
       <c r="G69" t="n">
-        <v>0.006991258369007768</v>
+        <v>0.01564230257413808</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1767504615821616</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="I69" t="n">
-        <v>0.00462847729159016</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>0.8513 ± 0.0009</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>0.2488 ± 0.0051</t>
+          <t>0.8121 ± 0.0097</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>0.4204 ± 0.0070</t>
+          <t>0.7948 ± 0.0156</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>0.1768 ± 0.0046</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0.8530750356181732</v>
+        <v>0.8455</v>
       </c>
       <c r="O69" t="n">
-        <v>0.001212077950855918</v>
+        <v>0.01039497741967513</v>
       </c>
       <c r="P69" t="n">
-        <v>0.1982972877374191</v>
+        <v>0.795035527912038</v>
       </c>
       <c r="Q69" t="n">
-        <v>0.01733491557879429</v>
+        <v>0.008164230429254637</v>
       </c>
       <c r="R69" t="n">
-        <v>0.4129480942886304</v>
+        <v>0.7569794205256127</v>
       </c>
       <c r="S69" t="n">
-        <v>0.01702310751314772</v>
+        <v>0.01940062770836523</v>
       </c>
       <c r="T69" t="n">
-        <v>0.1306632580599347</v>
+        <v>0.8455</v>
       </c>
       <c r="U69" t="n">
-        <v>0.01363324333261546</v>
+        <v>0.01039497741967513</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>0.8531 ± 0.0012</t>
+          <t>0.8455 ± 0.0104</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>0.1983 ± 0.0173</t>
+          <t>0.7950 ± 0.0082</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>0.4129 ± 0.0170</t>
+          <t>0.7570 ± 0.0194</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>0.1307 ± 0.0136</t>
+          <t>0.8455 ± 0.0104</t>
         </is>
       </c>
       <c r="Z69" t="n">
-        <v>-0.001739354123793113</v>
+        <v>0.002999999999999892</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.05052936704710131</v>
+        <v>0.01704222904517638</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.007419739977004791</v>
+        <v>0.03782804105365167</v>
       </c>
       <c r="AC69" t="n">
-        <v>0.04608720352222695</v>
+        <v>0.002999999999999892</v>
       </c>
       <c r="AD69" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8472158461294919</v>
+        <v>0.794</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0009310588989812209</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2760073032098657</v>
+        <v>0.7991552319401397</v>
       </c>
       <c r="E70" t="n">
-        <v>0.003654438442907095</v>
+        <v>0.01874904662857105</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4062323582339051</v>
+        <v>0.806926929702948</v>
       </c>
       <c r="G70" t="n">
-        <v>0.00489709142841155</v>
+        <v>0.01474411983059894</v>
       </c>
       <c r="H70" t="n">
-        <v>0.2090470103678455</v>
+        <v>0.794</v>
       </c>
       <c r="I70" t="n">
-        <v>0.004094394489595194</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>0.8472 ± 0.0009</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>0.2760 ± 0.0037</t>
+          <t>0.7992 ± 0.0187</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>0.4062 ± 0.0049</t>
+          <t>0.8069 ± 0.0147</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>0.2090 ± 0.0041</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.8443703498496122</v>
+        <v>0.7595</v>
       </c>
       <c r="O70" t="n">
-        <v>0.002155324629646412</v>
+        <v>0.04969071006402169</v>
       </c>
       <c r="P70" t="n">
-        <v>0.231243963132944</v>
+        <v>0.7579048370761177</v>
       </c>
       <c r="Q70" t="n">
-        <v>0.0137006705544126</v>
+        <v>0.0287833643353949</v>
       </c>
       <c r="R70" t="n">
-        <v>0.3707827247491188</v>
+        <v>0.7580658653685093</v>
       </c>
       <c r="S70" t="n">
-        <v>0.01709342485110321</v>
+        <v>0.01422434066153863</v>
       </c>
       <c r="T70" t="n">
-        <v>0.168115324527766</v>
+        <v>0.7595</v>
       </c>
       <c r="U70" t="n">
-        <v>0.01152280256385812</v>
+        <v>0.04969071006402169</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>0.8444 ± 0.0022</t>
+          <t>0.7595 ± 0.0497</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>0.2312 ± 0.0137</t>
+          <t>0.7579 ± 0.0288</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>0.3708 ± 0.0171</t>
+          <t>0.7581 ± 0.0142</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>0.1681 ± 0.0115</t>
+          <t>0.7595 ± 0.0497</t>
         </is>
       </c>
       <c r="Z70" t="n">
-        <v>0.002845496279879622</v>
+        <v>0.03450000000000009</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.04476334007692173</v>
+        <v>0.04125039486402204</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.03544963348478625</v>
+        <v>0.04886106433443871</v>
       </c>
       <c r="AC70" t="n">
-        <v>0.04093168584007956</v>
+        <v>0.03450000000000009</v>
       </c>
       <c r="AD70" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
@@ -11476,332 +11488,332 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7729420611049548</v>
+        <v>0.758</v>
       </c>
       <c r="C71" t="n">
-        <v>0.001604092504916999</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="D71" t="n">
-        <v>0.4111314934218446</v>
+        <v>0.7695653113724968</v>
       </c>
       <c r="E71" t="n">
-        <v>0.002269244542275589</v>
+        <v>0.1866093154578636</v>
       </c>
       <c r="F71" t="n">
-        <v>0.32188092350958</v>
+        <v>0.8530475252301031</v>
       </c>
       <c r="G71" t="n">
-        <v>0.001866083751005921</v>
+        <v>0.01193960102018576</v>
       </c>
       <c r="H71" t="n">
-        <v>0.5689106660985656</v>
+        <v>0.758</v>
       </c>
       <c r="I71" t="n">
-        <v>0.005812999479801975</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>0.7729 ± 0.0016</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>0.4111 ± 0.0023</t>
+          <t>0.7696 ± 0.1866</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>0.3219 ± 0.0019</t>
+          <t>0.8530 ± 0.0119</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>0.5689 ± 0.0058</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0.2876800696533165</v>
+        <v>0.7575000000000001</v>
       </c>
       <c r="O71" t="n">
-        <v>0.01325794881831392</v>
+        <v>0.01359125535858342</v>
       </c>
       <c r="P71" t="n">
-        <v>0.2721032847164263</v>
+        <v>0.7584484002038779</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.003645391628123934</v>
+        <v>0.005896346373562807</v>
       </c>
       <c r="R71" t="n">
-        <v>0.1586495092299866</v>
+        <v>0.7597922138141208</v>
       </c>
       <c r="S71" t="n">
-        <v>0.002465782440245203</v>
+        <v>0.005570077145047665</v>
       </c>
       <c r="T71" t="n">
-        <v>0.9553756568669224</v>
+        <v>0.7575000000000001</v>
       </c>
       <c r="U71" t="n">
-        <v>0.005611274864304836</v>
+        <v>0.01359125535858342</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>0.2877 ± 0.0133</t>
+          <t>0.7575 ± 0.0136</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>0.2721 ± 0.0036</t>
+          <t>0.7584 ± 0.0059</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>0.1586 ± 0.0025</t>
+          <t>0.7598 ± 0.0056</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>0.9554 ± 0.0056</t>
+          <t>0.7575 ± 0.0136</t>
         </is>
       </c>
       <c r="Z71" t="n">
-        <v>0.4852619914516383</v>
+        <v>0.0004999999999999449</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.1390282087054183</v>
+        <v>0.0111169111686189</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.1632314142795934</v>
+        <v>0.09325531141598231</v>
       </c>
       <c r="AC71" t="n">
-        <v>-0.3864649907683568</v>
+        <v>0.0004999999999999449</v>
       </c>
       <c r="AD71" t="inlineStr">
         <is>
-          <t>ForestDiffusion</t>
+          <t>TabDDPM</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GradientBoost</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.8653850720278614</v>
+        <v>0.8965</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0004897208981754782</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="D72" t="n">
-        <v>0.1722933021134507</v>
+        <v>0.8800945612919768</v>
       </c>
       <c r="E72" t="n">
-        <v>0.004133046767167164</v>
+        <v>0.01557076241163555</v>
       </c>
       <c r="F72" t="n">
-        <v>0.6012194836101217</v>
+        <v>0.8849723263768654</v>
       </c>
       <c r="G72" t="n">
-        <v>0.01161315896115709</v>
+        <v>0.01637849998720951</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1005681011219997</v>
+        <v>0.8965</v>
       </c>
       <c r="I72" t="n">
-        <v>0.002743294672201886</v>
+        <v>0.01106797181058934</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>0.8654 ± 0.0005</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0.1723 ± 0.0041</t>
+          <t>0.8801 ± 0.0156</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>0.6012 ± 0.0116</t>
+          <t>0.8850 ± 0.0164</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>0.1006 ± 0.0027</t>
+          <t>0.8965 ± 0.0111</t>
         </is>
       </c>
       <c r="N72" t="n">
-        <v>0.8555406047174292</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="O72" t="n">
-        <v>0.00377696765177999</v>
+        <v>0.008644201653259968</v>
       </c>
       <c r="P72" t="n">
-        <v>0.009733384613800168</v>
+        <v>0.8740589613153219</v>
       </c>
       <c r="Q72" t="n">
-        <v>0.006780845959806028</v>
+        <v>0.008504514563610215</v>
       </c>
       <c r="R72" t="n">
-        <v>0.1303637540525382</v>
+        <v>0.8717974753920386</v>
       </c>
       <c r="S72" t="n">
-        <v>0.0703114812688721</v>
+        <v>0.009961185756881206</v>
       </c>
       <c r="T72" t="n">
-        <v>0.005169720210197415</v>
+        <v>0.8845000000000001</v>
       </c>
       <c r="U72" t="n">
-        <v>0.003746991905084153</v>
+        <v>0.008644201653259968</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>0.8555 ± 0.0038</t>
+          <t>0.8845 ± 0.0086</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>0.0097 ± 0.0068</t>
+          <t>0.8741 ± 0.0085</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>0.1304 ± 0.0703</t>
+          <t>0.8718 ± 0.0100</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>0.0052 ± 0.0037</t>
+          <t>0.8845 ± 0.0086</t>
         </is>
       </c>
       <c r="Z72" t="n">
-        <v>0.009844467310432203</v>
+        <v>0.0119999999999999</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.1625599174996505</v>
+        <v>0.006035599976654926</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.4708557295575835</v>
+        <v>0.01317485098482685</v>
       </c>
       <c r="AC72" t="n">
-        <v>0.09539838091180228</v>
+        <v>0.0119999999999999</v>
       </c>
       <c r="AD72" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>LogReg</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8644649358872882</v>
+        <v>0.8905</v>
       </c>
       <c r="C73" t="n">
-        <v>0.001292019377334109</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2639376061713777</v>
+        <v>0.8613575595536576</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0296521977876718</v>
+        <v>0.00835629357808527</v>
       </c>
       <c r="F73" t="n">
-        <v>0.5445815044621426</v>
+        <v>0.8875770769739587</v>
       </c>
       <c r="G73" t="n">
-        <v>0.01990884968502404</v>
+        <v>0.009319454743331457</v>
       </c>
       <c r="H73" t="n">
-        <v>0.1754864365857122</v>
+        <v>0.8905</v>
       </c>
       <c r="I73" t="n">
-        <v>0.02609605447626427</v>
+        <v>0.004972144630058771</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>0.8645 ± 0.0013</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0.2639 ± 0.0297</t>
+          <t>0.8614 ± 0.0084</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>0.5446 ± 0.0199</t>
+          <t>0.8876 ± 0.0093</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>0.1755 ± 0.0261</t>
+          <t>0.8905 ± 0.0050</t>
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.8481953458920373</v>
+        <v>0.892</v>
       </c>
       <c r="O73" t="n">
-        <v>0.00515717857077356</v>
+        <v>0.007527726527090817</v>
       </c>
       <c r="P73" t="n">
-        <v>0.03961698089772425</v>
+        <v>0.8748453500252168</v>
       </c>
       <c r="Q73" t="n">
-        <v>0.01568461328391349</v>
+        <v>0.007458169753921906</v>
       </c>
       <c r="R73" t="n">
-        <v>0.1702923936811873</v>
+        <v>0.8792862472502394</v>
       </c>
       <c r="S73" t="n">
-        <v>0.02442399879718625</v>
+        <v>0.01186372439962882</v>
       </c>
       <c r="T73" t="n">
-        <v>0.02289447521658855</v>
+        <v>0.892</v>
       </c>
       <c r="U73" t="n">
-        <v>0.01039500870734086</v>
+        <v>0.007527726527090817</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>0.8482 ± 0.0052</t>
+          <t>0.8920 ± 0.0075</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>0.0396 ± 0.0157</t>
+          <t>0.8748 ± 0.0075</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>0.1703 ± 0.0244</t>
+          <t>0.8793 ± 0.0119</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>0.0229 ± 0.0104</t>
+          <t>0.8920 ± 0.0075</t>
         </is>
       </c>
       <c r="Z73" t="n">
-        <v>0.01626958999525097</v>
+        <v>-0.001500000000000057</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.2243206252736535</v>
+        <v>-0.01348779047155924</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.3742891107809553</v>
+        <v>0.008290829723719306</v>
       </c>
       <c r="AC73" t="n">
-        <v>0.1525919613691237</v>
+        <v>-0.001500000000000057</v>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -11812,780 +11824,780 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8635903118568941</v>
+        <v>0.8815</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0003809564049741432</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="D74" t="n">
-        <v>0.121804936464582</v>
+        <v>0.8395197032079371</v>
       </c>
       <c r="E74" t="n">
-        <v>0.00369981836688605</v>
+        <v>0.007183950573405901</v>
       </c>
       <c r="F74" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.8927447421022293</v>
       </c>
       <c r="G74" t="n">
-        <v>0.01145382697210849</v>
+        <v>0.01169636211175201</v>
       </c>
       <c r="H74" t="n">
-        <v>0.06790228660701605</v>
+        <v>0.8815</v>
       </c>
       <c r="I74" t="n">
-        <v>0.002191473549437678</v>
+        <v>0.004116363011742827</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>0.8636 ± 0.0004</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0.1218 ± 0.0037</t>
+          <t>0.8395 ± 0.0072</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>0.5911 ± 0.0115</t>
+          <t>0.8927 ± 0.0117</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>0.0679 ± 0.0022</t>
+          <t>0.8815 ± 0.0041</t>
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0.8606735792306475</v>
+        <v>0.89</v>
       </c>
       <c r="O74" t="n">
-        <v>0</v>
+        <v>0.006236095644623242</v>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>0.8622741608593515</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>0.0107043530784709</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>0.8831176570216487</v>
       </c>
       <c r="S74" t="n">
-        <v>0</v>
+        <v>0.01004847749414569</v>
       </c>
       <c r="T74" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="U74" t="n">
-        <v>0</v>
+        <v>0.006236095644623242</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>0.8607 ± 0.0000</t>
+          <t>0.8900 ± 0.0062</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>0.0000 ± 0.0000</t>
+          <t>0.8623 ± 0.0107</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>0.0000 ± 0.0000</t>
+          <t>0.8831 ± 0.0100</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>0.0000 ± 0.0000</t>
+          <t>0.8900 ± 0.0062</t>
         </is>
       </c>
       <c r="Z74" t="n">
-        <v>0.002916732626246588</v>
+        <v>-0.008500000000000063</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.121804936464582</v>
+        <v>-0.02275445765141437</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.5910960430943095</v>
+        <v>0.009627085080580633</v>
       </c>
       <c r="AC74" t="n">
-        <v>0.06790228660701605</v>
+        <v>-0.008500000000000063</v>
       </c>
       <c r="AD74" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LogReg</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8635467785341143</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0007481700690606898</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="D75" t="n">
-        <v>0.2388691165223189</v>
+        <v>0.8460496521431005</v>
       </c>
       <c r="E75" t="n">
-        <v>0.004564487931064464</v>
+        <v>0.01294479429530151</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5359686608772588</v>
+        <v>0.865010991243126</v>
       </c>
       <c r="G75" t="n">
-        <v>0.00934558839892455</v>
+        <v>0.02161817607890089</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1536855560289732</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="I75" t="n">
-        <v>0.003128072545874311</v>
+        <v>0.008164965809277268</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>0.8635 ± 0.0007</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>0.2389 ± 0.0046</t>
+          <t>0.8460 ± 0.0129</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>0.5360 ± 0.0093</t>
+          <t>0.8650 ± 0.0216</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>0.1537 ± 0.0031</t>
+          <t>0.8800 ± 0.0082</t>
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.8601393066328953</v>
+        <v>0.867</v>
       </c>
       <c r="O75" t="n">
-        <v>0.0005102049190908339</v>
+        <v>0.008232726023485654</v>
       </c>
       <c r="P75" t="n">
-        <v>0.001013054635224362</v>
+        <v>0.8317730476364493</v>
       </c>
       <c r="Q75" t="n">
-        <v>0.001075337642532265</v>
+        <v>0.009232178771023704</v>
       </c>
       <c r="R75" t="n">
-        <v>0.08009597637504615</v>
+        <v>0.8361931687425281</v>
       </c>
       <c r="S75" t="n">
-        <v>0.05699063662778444</v>
+        <v>0.02217992328586535</v>
       </c>
       <c r="T75" t="n">
-        <v>0.0005112910097997443</v>
+        <v>0.867</v>
       </c>
       <c r="U75" t="n">
-        <v>0.0005434207206280071</v>
+        <v>0.008232726023485654</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>0.8601 ± 0.0005</t>
+          <t>0.8670 ± 0.0082</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>0.0010 ± 0.0011</t>
+          <t>0.8318 ± 0.0092</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>0.0801 ± 0.0570</t>
+          <t>0.8362 ± 0.0222</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>0.0005 ± 0.0005</t>
+          <t>0.8670 ± 0.0082</t>
         </is>
       </c>
       <c r="Z75" t="n">
-        <v>0.003407471901219039</v>
+        <v>0.01300000000000012</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.2378560618870945</v>
+        <v>0.01427660450665114</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.4558726845022126</v>
+        <v>0.02881782250059783</v>
       </c>
       <c r="AC75" t="n">
-        <v>0.1531742650191734</v>
+        <v>0.01300000000000012</v>
       </c>
       <c r="AD75" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>GradientBoost</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.8631213392433116</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0006492744915581773</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="D76" t="n">
-        <v>0.2907324908296564</v>
+        <v>0.8454437371166996</v>
       </c>
       <c r="E76" t="n">
-        <v>0.01155213366104772</v>
+        <v>0.009700800200490399</v>
       </c>
       <c r="F76" t="n">
-        <v>0.5229396461150038</v>
+        <v>0.8608277232976554</v>
       </c>
       <c r="G76" t="n">
-        <v>0.006564777307101441</v>
+        <v>0.02216917078425409</v>
       </c>
       <c r="H76" t="n">
-        <v>0.2015338730293992</v>
+        <v>0.8775000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>0.01144868243932203</v>
+        <v>0.008249579113843062</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>0.8631 ± 0.0006</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0.2907 ± 0.0116</t>
+          <t>0.8454 ± 0.0097</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>0.5229 ± 0.0066</t>
+          <t>0.8608 ± 0.0222</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>0.2015 ± 0.0114</t>
+          <t>0.8775 ± 0.0082</t>
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.8605687034984962</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="O76" t="n">
-        <v>0.0001207060313439867</v>
+        <v>0.01173787790777268</v>
       </c>
       <c r="P76" t="n">
-        <v>0.0003115709756448731</v>
+        <v>0.8356806037864141</v>
       </c>
       <c r="Q76" t="n">
-        <v>0.0004643040521165739</v>
+        <v>0.01296409706277128</v>
       </c>
       <c r="R76" t="n">
-        <v>0.08583333333333334</v>
+        <v>0.8278647307416687</v>
       </c>
       <c r="S76" t="n">
-        <v>0.1153527199505933</v>
+        <v>0.01624445982897337</v>
       </c>
       <c r="T76" t="n">
-        <v>0.0001562278085499219</v>
+        <v>0.8560000000000001</v>
       </c>
       <c r="U76" t="n">
-        <v>0.0002329387795321222</v>
+        <v>0.01173787790777268</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>0.8606 ± 0.0001</t>
+          <t>0.8560 ± 0.0117</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>0.0003 ± 0.0005</t>
+          <t>0.8357 ± 0.0130</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>0.0858 ± 0.1154</t>
+          <t>0.8279 ± 0.0162</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>0.0002 ± 0.0002</t>
+          <t>0.8560 ± 0.0117</t>
         </is>
       </c>
       <c r="Z76" t="n">
-        <v>0.002552635744815346</v>
+        <v>0.02149999999999996</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.2904209198540115</v>
+        <v>0.009763133330285556</v>
       </c>
       <c r="AB76" t="n">
-        <v>0.4371063127816704</v>
+        <v>0.03296299255598678</v>
       </c>
       <c r="AC76" t="n">
-        <v>0.2013776452208493</v>
+        <v>0.02149999999999996</v>
       </c>
       <c r="AD76" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ExtraTrees</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.8585760645876208</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0008837008421368494</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2542904020111528</v>
+        <v>0.835494258836275</v>
       </c>
       <c r="E77" t="n">
-        <v>0.004123268112439032</v>
+        <v>0.01145355069185408</v>
       </c>
       <c r="F77" t="n">
-        <v>0.4792228106524696</v>
+        <v>0.847039871734004</v>
       </c>
       <c r="G77" t="n">
-        <v>0.0086336230115462</v>
+        <v>0.01822934405953743</v>
       </c>
       <c r="H77" t="n">
-        <v>0.1730720068172134</v>
+        <v>0.8724999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>0.003012275509749968</v>
+        <v>0.007168604389202195</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>0.8586 ± 0.0009</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0.2543 ± 0.0041</t>
+          <t>0.8355 ± 0.0115</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>0.4792 ± 0.0086</t>
+          <t>0.8470 ± 0.0182</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>0.1731 ± 0.0030</t>
+          <t>0.8725 ± 0.0072</t>
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0.8585087858160518</v>
+        <v>0.8725000000000002</v>
       </c>
       <c r="O77" t="n">
-        <v>0.000923277687889107</v>
+        <v>0.0088975652100261</v>
       </c>
       <c r="P77" t="n">
-        <v>0.00294689508052617</v>
+        <v>0.8390546705140765</v>
       </c>
       <c r="Q77" t="n">
-        <v>0.001366092119697046</v>
+        <v>0.01296203029878578</v>
       </c>
       <c r="R77" t="n">
-        <v>0.08194104491453391</v>
+        <v>0.8446664360507107</v>
       </c>
       <c r="S77" t="n">
-        <v>0.01995972588599695</v>
+        <v>0.01936142229675867</v>
       </c>
       <c r="T77" t="n">
-        <v>0.001505467973299247</v>
+        <v>0.8725000000000002</v>
       </c>
       <c r="U77" t="n">
-        <v>0.0007106942765628066</v>
+        <v>0.0088975652100261</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>0.8585 ± 0.0009</t>
+          <t>0.8725 ± 0.0089</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>0.0029 ± 0.0014</t>
+          <t>0.8391 ± 0.0130</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>0.0819 ± 0.0200</t>
+          <t>0.8447 ± 0.0194</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>0.0015 ± 0.0007</t>
+          <t>0.8725 ± 0.0089</t>
         </is>
       </c>
       <c r="Z77" t="n">
-        <v>6.727877156897932e-05</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.2513435069306267</v>
+        <v>-0.003560411677801412</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.3972817657379357</v>
+        <v>0.00237343568329329</v>
       </c>
       <c r="AC77" t="n">
-        <v>0.1715665388439142</v>
+        <v>-2.220446049250313e-16</v>
       </c>
       <c r="AD77" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DecisionTree</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.8577034193446256</v>
+        <v>0.8665</v>
       </c>
       <c r="C78" t="n">
-        <v>0.001100478021426305</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2518109924417331</v>
+        <v>0.8492915770742749</v>
       </c>
       <c r="E78" t="n">
-        <v>0.00902185699517897</v>
+        <v>0.01093808385599739</v>
       </c>
       <c r="F78" t="n">
-        <v>0.4710247118621849</v>
+        <v>0.8431685063356953</v>
       </c>
       <c r="G78" t="n">
-        <v>0.01001864628250197</v>
+        <v>0.01341255506478664</v>
       </c>
       <c r="H78" t="n">
-        <v>0.171964209629314</v>
+        <v>0.8665</v>
       </c>
       <c r="I78" t="n">
-        <v>0.008237907025316163</v>
+        <v>0.008834905520465721</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>0.8577 ± 0.0011</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0.2518 ± 0.0090</t>
+          <t>0.8493 ± 0.0109</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>0.4710 ± 0.0100</t>
+          <t>0.8432 ± 0.0134</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>0.1720 ± 0.0082</t>
+          <t>0.8665 ± 0.0088</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.7278692417286687</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="O78" t="n">
-        <v>0.02918620347758178</v>
+        <v>0.01370320319406299</v>
       </c>
       <c r="P78" t="n">
-        <v>0.1496721451029945</v>
+        <v>0.8513079585760513</v>
       </c>
       <c r="Q78" t="n">
-        <v>0.02576138707150587</v>
+        <v>0.01472495814796158</v>
       </c>
       <c r="R78" t="n">
-        <v>0.1333702775690188</v>
+        <v>0.8452658116236673</v>
       </c>
       <c r="S78" t="n">
-        <v>0.018098328120112</v>
+        <v>0.01704866229207197</v>
       </c>
       <c r="T78" t="n">
-        <v>0.1745916773185627</v>
+        <v>0.8640000000000001</v>
       </c>
       <c r="U78" t="n">
-        <v>0.0448853839259956</v>
+        <v>0.01370320319406299</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
-          <t>0.7279 ± 0.0292</t>
+          <t>0.8640 ± 0.0137</t>
         </is>
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>0.1497 ± 0.0258</t>
+          <t>0.8513 ± 0.0147</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>0.1334 ± 0.0181</t>
+          <t>0.8453 ± 0.0170</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>0.1746 ± 0.0449</t>
+          <t>0.8640 ± 0.0137</t>
         </is>
       </c>
       <c r="Z78" t="n">
-        <v>0.1298341776159568</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.1021388473387386</v>
+        <v>-0.00201638150177641</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.3376544342931661</v>
+        <v>-0.002097305287972029</v>
       </c>
       <c r="AC78" t="n">
-        <v>-0.00262746768924868</v>
+        <v>0.002499999999999947</v>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ExtraTrees</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.8513356814943801</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0009037427725112313</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="D79" t="n">
-        <v>0.2488266547845204</v>
+        <v>0.8120777569572144</v>
       </c>
       <c r="E79" t="n">
-        <v>0.00511286061119995</v>
+        <v>0.009746337201211541</v>
       </c>
       <c r="F79" t="n">
-        <v>0.4203678342656352</v>
+        <v>0.7948074615792644</v>
       </c>
       <c r="G79" t="n">
-        <v>0.006991258369007768</v>
+        <v>0.01564230257413808</v>
       </c>
       <c r="H79" t="n">
-        <v>0.1767504615821616</v>
+        <v>0.8484999999999999</v>
       </c>
       <c r="I79" t="n">
-        <v>0.00462847729159016</v>
+        <v>0.008514693182963209</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>0.8513 ± 0.0009</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0.2488 ± 0.0051</t>
+          <t>0.8121 ± 0.0097</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>0.4204 ± 0.0070</t>
+          <t>0.7948 ± 0.0156</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>0.1768 ± 0.0046</t>
+          <t>0.8485 ± 0.0085</t>
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0.8518679753047333</v>
+        <v>0.8644999999999999</v>
       </c>
       <c r="O79" t="n">
-        <v>0.001281820538095891</v>
+        <v>0.005986094998689329</v>
       </c>
       <c r="P79" t="n">
-        <v>0.01348859401639657</v>
+        <v>0.8397690328049215</v>
       </c>
       <c r="Q79" t="n">
-        <v>0.003660832807467163</v>
+        <v>0.008733820353619547</v>
       </c>
       <c r="R79" t="n">
-        <v>0.0927921871297462</v>
+        <v>0.8344313125015056</v>
       </c>
       <c r="S79" t="n">
-        <v>0.01738189120774628</v>
+        <v>0.01128806302708654</v>
       </c>
       <c r="T79" t="n">
-        <v>0.007285896889646357</v>
+        <v>0.8644999999999999</v>
       </c>
       <c r="U79" t="n">
-        <v>0.002043437308587493</v>
+        <v>0.005986094998689329</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
-          <t>0.8519 ± 0.0013</t>
+          <t>0.8645 ± 0.0060</t>
         </is>
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>0.0135 ± 0.0037</t>
+          <t>0.8398 ± 0.0087</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>0.0928 ± 0.0174</t>
+          <t>0.8344 ± 0.0113</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>0.0073 ± 0.0020</t>
+          <t>0.8645 ± 0.0060</t>
         </is>
       </c>
       <c r="Z79" t="n">
-        <v>-0.000532293810353246</v>
+        <v>-0.01600000000000001</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.2353380607681239</v>
+        <v>-0.02769127584770714</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.327575647135889</v>
+        <v>-0.03962385092224119</v>
       </c>
       <c r="AC79" t="n">
-        <v>0.1694645646925153</v>
+        <v>-0.01600000000000001</v>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>DecisionTree</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.8472158461294919</v>
+        <v>0.794</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0009310588989812209</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2760073032098657</v>
+        <v>0.7991552319401397</v>
       </c>
       <c r="E80" t="n">
-        <v>0.003654438442907095</v>
+        <v>0.01874904662857105</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4062323582339051</v>
+        <v>0.806926929702948</v>
       </c>
       <c r="G80" t="n">
-        <v>0.00489709142841155</v>
+        <v>0.01474411983059894</v>
       </c>
       <c r="H80" t="n">
-        <v>0.2090470103678455</v>
+        <v>0.794</v>
       </c>
       <c r="I80" t="n">
-        <v>0.004094394489595194</v>
+        <v>0.02786873995477129</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>0.8472 ± 0.0009</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0.2760 ± 0.0037</t>
+          <t>0.7992 ± 0.0187</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>0.4062 ± 0.0049</t>
+          <t>0.8069 ± 0.0147</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>0.2090 ± 0.0041</t>
+          <t>0.7940 ± 0.0279</t>
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.8458029919265474</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="O80" t="n">
-        <v>0.001758857064936351</v>
+        <v>0.02608213522274928</v>
       </c>
       <c r="P80" t="n">
-        <v>0.02865520606143544</v>
+        <v>0.7869109458280485</v>
       </c>
       <c r="Q80" t="n">
-        <v>0.004073347901818477</v>
+        <v>0.02195959925702665</v>
       </c>
       <c r="R80" t="n">
-        <v>0.1172782293793152</v>
+        <v>0.81003273111726</v>
       </c>
       <c r="S80" t="n">
-        <v>0.01220490747916881</v>
+        <v>0.0191996780030147</v>
       </c>
       <c r="T80" t="n">
-        <v>0.01634710978554182</v>
+        <v>0.7695000000000001</v>
       </c>
       <c r="U80" t="n">
-        <v>0.002488848681350422</v>
+        <v>0.02608213522274928</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
-          <t>0.8458 ± 0.0018</t>
+          <t>0.7695 ± 0.0261</t>
         </is>
       </c>
       <c r="W80" t="inlineStr">
         <is>
-          <t>0.0287 ± 0.0041</t>
+          <t>0.7869 ± 0.0220</t>
         </is>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>0.1173 ± 0.0122</t>
+          <t>0.8100 ± 0.0192</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>0.0163 ± 0.0025</t>
+          <t>0.7695 ± 0.0261</t>
         </is>
       </c>
       <c r="Z80" t="n">
-        <v>0.001412854202944458</v>
+        <v>0.02449999999999997</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.2473520971484303</v>
+        <v>0.01224428611209116</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.2889541288545898</v>
+        <v>-0.003105801414312048</v>
       </c>
       <c r="AC80" t="n">
-        <v>0.1926999005823037</v>
+        <v>0.02449999999999997</v>
       </c>
       <c r="AD80" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -12596,108 +12608,108 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7729420611049548</v>
+        <v>0.758</v>
       </c>
       <c r="C81" t="n">
-        <v>0.001604092504916999</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="D81" t="n">
-        <v>0.4111314934218446</v>
+        <v>0.7695653113724968</v>
       </c>
       <c r="E81" t="n">
-        <v>0.002269244542275589</v>
+        <v>0.1866093154578636</v>
       </c>
       <c r="F81" t="n">
-        <v>0.32188092350958</v>
+        <v>0.8530475252301031</v>
       </c>
       <c r="G81" t="n">
-        <v>0.001866083751005921</v>
+        <v>0.01193960102018576</v>
       </c>
       <c r="H81" t="n">
-        <v>0.5689106660985656</v>
+        <v>0.758</v>
       </c>
       <c r="I81" t="n">
-        <v>0.005812999479801975</v>
+        <v>0.1786710198474653</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>0.7729 ± 0.0016</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0.4111 ± 0.0023</t>
+          <t>0.7696 ± 0.1866</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>0.3219 ± 0.0019</t>
+          <t>0.8530 ± 0.0119</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>0.5689 ± 0.0058</t>
+          <t>0.7580 ± 0.1787</t>
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.8468933037834414</v>
+        <v>0.5515</v>
       </c>
       <c r="O81" t="n">
-        <v>0.02330599669903018</v>
+        <v>0.2603528588495066</v>
       </c>
       <c r="P81" t="n">
-        <v>0.003204708991913499</v>
+        <v>0.5707855242882436</v>
       </c>
       <c r="Q81" t="n">
-        <v>0.004453870499127896</v>
+        <v>0.2617419349196998</v>
       </c>
       <c r="R81" t="n">
-        <v>0.2309094898784584</v>
+        <v>0.864237257200078</v>
       </c>
       <c r="S81" t="n">
-        <v>0.3871458237319818</v>
+        <v>0.01629017285189378</v>
       </c>
       <c r="T81" t="n">
-        <v>0.002130379207498935</v>
+        <v>0.5515</v>
       </c>
       <c r="U81" t="n">
-        <v>0.003106427635731815</v>
+        <v>0.2603528588495066</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
-          <t>0.8469 ± 0.0233</t>
+          <t>0.5515 ± 0.2604</t>
         </is>
       </c>
       <c r="W81" t="inlineStr">
         <is>
-          <t>0.0032 ± 0.0045</t>
+          <t>0.5708 ± 0.2617</t>
         </is>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>0.2309 ± 0.3871</t>
+          <t>0.8642 ± 0.0163</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>0.0021 ± 0.0031</t>
+          <t>0.5515 ± 0.2604</t>
         </is>
       </c>
       <c r="Z81" t="n">
-        <v>-0.07395124267848663</v>
+        <v>0.2065</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.4079267844299311</v>
+        <v>0.1987797870842533</v>
       </c>
       <c r="AB81" t="n">
-        <v>0.09097143363112159</v>
+        <v>-0.01118973196997497</v>
       </c>
       <c r="AC81" t="n">
-        <v>0.5667802868910666</v>
+        <v>0.2065</v>
       </c>
       <c r="AD81" t="inlineStr">
         <is>
-          <t>TabDDPM</t>
+          <t>ForestDiffusion</t>
         </is>
       </c>
     </row>
@@ -12716,27 +12728,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
@@ -12863,16 +12875,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.009182167167959453</v>
+        <v>0.02165</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2281061757594843</v>
+        <v>0.04384729193677982</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3771657290369433</v>
+        <v>0.1013921766280741</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1768328362448516</v>
+        <v>0.02165</v>
       </c>
     </row>
     <row r="9">
@@ -12882,16 +12894,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05957139464935882</v>
+        <v>0.02539999999999996</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001217463823266921</v>
+        <v>0.01715890938596775</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08879722316143546</v>
+        <v>0.003923032693450445</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.06541542394546231</v>
+        <v>0.02539999999999996</v>
       </c>
     </row>
   </sheetData>
@@ -12909,152 +12921,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -14195,152 +14207,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -15481,152 +15493,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -16767,152 +16779,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -18053,152 +18065,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
@@ -19339,152 +19351,152 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TRTR</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TRTR</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TRTR</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TRTR</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TRTR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TRTR</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TRTR</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TRTR</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TRTR</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Mean_TSTR</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Accuracy Std_TSTR</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>F1 Mean_TSTR</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>F1 Std_TSTR</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Precision Mean_TSTR</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Precision Std_TSTR</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Recall Mean_TSTR</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Recall Std_TSTR</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Accuracy (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>F1 (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Precision (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Recall (Mean±Std)_TSTR</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Accuracy_Drop</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>F1_Drop</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Precision_Drop</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Recall_Drop</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Synthetic_Model</t>
         </is>
